--- a/output/stock_quant_scores/RACE_balance_df.xlsx
+++ b/output/stock_quant_scores/RACE_balance_df.xlsx
@@ -1837,25 +1837,35 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>2630011000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>2037612000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>2205898000</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>2192453000</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>4652089000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1872,7 +1882,9 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>1326107000</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -1881,7 +1893,9 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>6863505000</v>
+      </c>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
@@ -1901,11 +1915,15 @@
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>3363719000</v>
+      </c>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
+      <c r="BR6" t="n">
+        <v>540575000</v>
+      </c>
       <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
@@ -1917,7 +1935,9 @@
       <c r="CA6" t="inlineStr"/>
       <c r="CB6" t="inlineStr"/>
       <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
+      <c r="CD6" t="n">
+        <v>1344146000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
